--- a/submission/knowledge/A05-武汉行程规划师/武汉行程规划师QA导入表.xlsx
+++ b/submission/knowledge/A05-武汉行程规划师/武汉行程规划师QA导入表.xlsx
@@ -367,6 +367,601 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花季怎么排？</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大校园预约和东湖樱园分开。不要一上午两个。失败改听涛或江滩。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三天够不够三镇？</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">够，建议一镇一天。木兰单独一天。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三日</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">明天下雨？</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">改室内馆和商场过早。游船问预约官是否取消。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高铁停四小时？</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只排出站那一镇一个点。武昌站对黄鹤楼相对近。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过境</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">周一来有什么闭？</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博、古琴台、晴川阁、辛亥南区常闭。辛亥红楼是周二闭。以各馆当天为准。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">星期</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼进不去？</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩、听涛、已预约省博。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">满载</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">人在汉口站半天？</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路+江滩。不要再承诺登黄鹤楼。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉口半天</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只在汉阳？</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">古琴台+晴川方向。问清是否周一闭馆。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉阳半天</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白天爬楼晚上还能游船吗？</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可以留一项夜游，预留过江和末班。四件事不要全订。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜游</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太累了？</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">取消夜游，改江滩或回酒店。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">放弃</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉站半天去黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">偏东，时间紧。可改东湖听涛或只排一个点。</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉站</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两天带老人怎么排？</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尽量一镇一天。少台阶：江滩、听涛、室内馆。黄鹤楼量力。</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">老人</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武大没约上怎么改？</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">听涛、江滩或已预约的东湖樱园。不买黄牛。不要一上午硬塞黄鹤楼+樱园+武大。</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">樱花</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">省博和辛亥同一天？</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可以，但要算武昌移动时间，且预约规则不同。问清星期几：省博周一常闭，辛亥南北区错峰休。</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">馆</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">天河落地只剩半天？</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要承诺登顶黄鹤楼。可江滩或汉口一镇，细接驳问管家。</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">机场</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">晚上十点才到？</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">只排江滩看照明。轮渡夜间不当回家方式。</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜达</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">第三天去木兰？</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可以单独一天。不要塞进黄鹤楼上午。咨询电话区政府信息公开为027-61502718。</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">三日</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高温红色预警还爬楼吗？</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">压缩正午户外。上午或只游园。中暑加重120，应急助手给短指令。</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">高温</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">周一怎么排三镇？</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">不要排省博、古琴台、晴川阁、辛亥南区为主线。改黄鹤楼、江滩、听涛、汉口室内。仍以当天公告为准。</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">周一</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">户部巷放哪段？</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄鹤楼日场前就近，或改商场店。不要为打卡耗半天。店问美食顾问。</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过早</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">想坐轮渡体验？</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">插在白天两镇之间，轻装。武中线公开报道约6:30—20:00、1.5元，以当天为准。夜游船是另一产品。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">轮渡</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">开会间隙两小时？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉街或江汉路室内。不安排酒局和跨江登楼。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">商务</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">带婴儿推车？</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">优先江滩、听涛、汉街。蛇山台阶多，黄鹤楼缩短。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">推车</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">带狗怎么排？</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">多数文物园限制，先问景区公众号。不要默认黄鹤楼可带。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">宠物</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">白天东湖晚上夜上黄鹤楼？</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">可以留这一项，预留过江和末班。不要再叠加游船和晴川夜游。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">夜场</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住光谷怎么排景点？</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">去黄鹤楼要穿城。一天只排一个主点，或把东湖听涛当主。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">住宿</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉站出站半天？</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">偏东，可听涛。不要同时磨山樱园+落雁+黄鹤楼。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">武汉站</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">雨天室内清单？</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">已预约省博、商场、汉街。没预约不要承诺插队进馆。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">室内</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">一天不想爬楼？</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江滩+听涛+汉口步行。古琴台平地相对友好，仍问星期一。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">无楼</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">学生两日研学？</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">D1辛亥或省博（规则不同），D2知音/汉绣讲解。少十个打卡点。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">研学</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">日场黄鹤楼晚上灯光秀？</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光秀多在江滩免费看，不必再买夜场。四件套只选一项夜游。</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">灯光</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汉口站停四小时？</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">江汉路+江滩。不要折返登楼。</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">过境</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">规划里黄鹤楼满了？</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">立刻改江滩、听涛、已预约的馆。不编「今天不堵」。</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">满载</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">几点末班地铁？</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问交通住宿管家。我只留「预留回程」。</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">帮我订夜游票。</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">问活动预约官和商户助手。我只把夜游放进时间窗。</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">边界</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>